--- a/ai_logs/PhanVanBao_Ai_Log _.xlsx
+++ b/ai_logs/PhanVanBao_Ai_Log _.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\NHOM_04_LAB211_TicketBooking\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1800DA-DDDA-4D04-B278-09731D14E492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3050ADDF-BBFF-4752-9BA7-0BA4CE952483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="263">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -823,6 +823,9 @@
   </si>
   <si>
     <t>Thêm bước kiểm tra null cho các field trước khi update.</t>
+  </si>
+  <si>
+    <t>ddd</t>
   </si>
 </sst>
 </file>
@@ -985,7 +988,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1022,22 +1025,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1047,10 +1034,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1058,6 +1042,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1372,14 +1372,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1618,28 +1618,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:8" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -1746,158 +1746,158 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24">
+      <c r="A7" s="18">
         <v>4</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G7" s="24" t="s">
+      <c r="G7" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="H7" s="24" t="s">
+      <c r="H7" s="18" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="123.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24">
+      <c r="A8" s="18">
         <v>5</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="18" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="24">
+      <c r="A9" s="18">
         <v>6</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="G9" s="24" t="s">
+      <c r="G9" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="H9" s="24" t="s">
+      <c r="H9" s="18" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="24">
+      <c r="A10" s="18">
         <v>7</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="G10" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="H10" s="24" t="s">
+      <c r="H10" s="18" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="24">
+      <c r="A11" s="18">
         <v>8</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="F11" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="G11" s="24" t="s">
+      <c r="G11" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="H11" s="24" t="s">
+      <c r="H11" s="18" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="24">
+      <c r="A12" s="18">
         <v>9</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="D12" s="24" t="s">
+      <c r="D12" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="F12" s="24" t="s">
+      <c r="F12" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="H12" s="24" t="s">
+      <c r="H12" s="18" t="s">
         <v>179</v>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       <c r="A13" s="9">
         <v>10</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="18" t="s">
         <v>52</v>
       </c>
       <c r="C13" s="9" t="s">
@@ -1949,7 +1949,7 @@
       <c r="G14" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="H14" s="25" t="s">
+      <c r="H14" s="19" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       <c r="F15" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="19" t="s">
         <v>215</v>
       </c>
       <c r="H15" s="9" t="s">
@@ -1998,7 +1998,7 @@
       <c r="F16" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="G16" s="26" t="s">
+      <c r="G16" s="20" t="s">
         <v>221</v>
       </c>
       <c r="H16" s="9" t="s">
@@ -2024,88 +2024,88 @@
       <c r="F17" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="G17" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="H17" s="25" t="s">
+      <c r="H17" s="19" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="27">
+      <c r="A18" s="21">
         <v>15</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="27" t="s">
+      <c r="C18" s="21" t="s">
         <v>229</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="21" t="s">
         <v>230</v>
       </c>
-      <c r="E18" s="27" t="s">
+      <c r="E18" s="21" t="s">
         <v>231</v>
       </c>
-      <c r="F18" s="27" t="s">
+      <c r="F18" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="G18" s="28" t="s">
+      <c r="G18" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="H18" s="28" t="s">
+      <c r="H18" s="19" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="27">
+      <c r="A19" s="21">
         <v>16</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="21" t="s">
         <v>235</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="E19" s="27" t="s">
+      <c r="E19" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="F19" s="27" t="s">
+      <c r="F19" s="21" t="s">
         <v>238</v>
       </c>
-      <c r="G19" s="28" t="s">
+      <c r="G19" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="H19" s="28" t="s">
+      <c r="H19" s="19" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="29">
+      <c r="A20" s="22">
         <v>17</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" s="22" t="s">
         <v>241</v>
       </c>
-      <c r="D20" s="29" t="s">
+      <c r="D20" s="22" t="s">
         <v>242</v>
       </c>
-      <c r="E20" s="29" t="s">
+      <c r="E20" s="22" t="s">
         <v>243</v>
       </c>
-      <c r="F20" s="29" t="s">
+      <c r="F20" s="22" t="s">
         <v>244</v>
       </c>
-      <c r="G20" s="29" t="s">
+      <c r="G20" s="22" t="s">
         <v>245</v>
       </c>
-      <c r="H20" s="29" t="s">
+      <c r="H20" s="22" t="s">
         <v>246</v>
       </c>
     </row>
@@ -2192,24 +2192,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
     </row>
     <row r="3" spans="1:6" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -2232,229 +2232,231 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="30">
+      <c r="A4" s="23">
         <v>1</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="23" t="s">
         <v>211</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="23" t="s">
         <v>210</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="23" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="30">
+      <c r="A5" s="23">
         <v>2</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="23" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="30">
+      <c r="A6" s="23">
         <v>3</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="23" t="s">
         <v>203</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="23" t="s">
         <v>202</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="23" t="s">
         <v>201</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="23" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="30">
+      <c r="A7" s="23">
         <v>4</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="23" t="s">
         <v>199</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="E7" s="30" t="s">
+      <c r="E7" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="F7" s="30" t="s">
+      <c r="F7" s="23" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="30">
+      <c r="A8" s="23">
         <v>5</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="F8" s="30" t="s">
+      <c r="F8" s="23" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="30">
+      <c r="A9" s="23">
         <v>6</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="D9" s="30" t="s">
+      <c r="D9" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="E9" s="30" t="s">
+      <c r="E9" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="F9" s="30" t="s">
+      <c r="F9" s="23" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="30">
+      <c r="A10" s="23">
         <v>7</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="F10" s="30" t="s">
+      <c r="F10" s="23" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="30">
+      <c r="A11" s="23">
         <v>8</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C11" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="E11" s="30" t="s">
+      <c r="E11" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="F11" s="30" t="s">
+      <c r="F11" s="23" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="29">
+      <c r="A12" s="22">
         <v>9</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="22" t="s">
         <v>247</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="22" t="s">
         <v>248</v>
       </c>
-      <c r="D12" s="29" t="s">
+      <c r="D12" s="22" t="s">
         <v>249</v>
       </c>
-      <c r="E12" s="29" t="s">
+      <c r="E12" s="22" t="s">
         <v>250</v>
       </c>
-      <c r="F12" s="29" t="s">
+      <c r="F12" s="22" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="29">
+      <c r="A13" s="22">
         <v>10</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="22" t="s">
         <v>252</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="D13" s="22" t="s">
         <v>256</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="E13" s="22" t="s">
         <v>258</v>
       </c>
-      <c r="F13" s="29" t="s">
+      <c r="F13" s="22" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="29">
+      <c r="A14" s="22">
         <v>11</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="22" t="s">
         <v>253</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="22" t="s">
         <v>255</v>
       </c>
-      <c r="D14" s="29" t="s">
+      <c r="D14" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="E14" s="29" t="s">
+      <c r="E14" s="22" t="s">
         <v>259</v>
       </c>
-      <c r="F14" s="29" t="s">
+      <c r="F14" s="22" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
+      <c r="C15" s="7" t="s">
+        <v>262</v>
+      </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -2547,7 +2549,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>73</v>
       </c>
@@ -2623,20 +2625,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">

--- a/ai_logs/PhanVanBao_Ai_Log _.xlsx
+++ b/ai_logs/PhanVanBao_Ai_Log _.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\NHOM_04_LAB211_TicketBooking\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3050ADDF-BBFF-4752-9BA7-0BA4CE952483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCB2B31-431D-45A2-BEB8-7D5F4209EA95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="262">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -823,9 +823,6 @@
   </si>
   <si>
     <t>Thêm bước kiểm tra null cho các field trước khi update.</t>
-  </si>
-  <si>
-    <t>ddd</t>
   </si>
 </sst>
 </file>
@@ -2454,9 +2451,7 @@
     <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
-      <c r="C15" s="7" t="s">
-        <v>262</v>
-      </c>
+      <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>

--- a/ai_logs/PhanVanBao_Ai_Log _.xlsx
+++ b/ai_logs/PhanVanBao_Ai_Log _.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\NHOM_04_LAB211_TicketBooking\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCB2B31-431D-45A2-BEB8-7D5F4209EA95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2C872C-7743-4AA8-86F7-8B4F43F5C9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="263">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -823,6 +823,9 @@
   </si>
   <si>
     <t>Thêm bước kiểm tra null cho các field trước khi update.</t>
+  </si>
+  <si>
+    <t>dddddddd</t>
   </si>
 </sst>
 </file>
@@ -2110,7 +2113,9 @@
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
+      <c r="D21" s="7" t="s">
+        <v>262</v>
+      </c>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>

--- a/ai_logs/PhanVanBao_Ai_Log _.xlsx
+++ b/ai_logs/PhanVanBao_Ai_Log _.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\NHOM_04_LAB211_TicketBooking\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2C872C-7743-4AA8-86F7-8B4F43F5C9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B5E62C-0035-4D81-B8E2-E61296E39070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="266">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -825,7 +825,16 @@
     <t>Thêm bước kiểm tra null cho các field trước khi update.</t>
   </si>
   <si>
-    <t>dddddddd</t>
+    <t>hellllllo</t>
+  </si>
+  <si>
+    <t>ddewfe</t>
+  </si>
+  <si>
+    <t>efwsefwf</t>
+  </si>
+  <si>
+    <t>fewewwef</t>
   </si>
 </sst>
 </file>
@@ -1043,18 +1052,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1372,7 +1381,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="25"/>
@@ -1618,7 +1627,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="25"/>
@@ -1630,7 +1639,7 @@
       <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="24" t="s">
         <v>40</v>
       </c>
       <c r="B2" s="25"/>
@@ -2112,12 +2121,18 @@
     <row r="21" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
+      <c r="C21" s="7" t="s">
+        <v>263</v>
+      </c>
       <c r="D21" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
+      <c r="E21" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>265</v>
+      </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
     </row>
@@ -2194,7 +2209,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="28" t="s">
         <v>65</v>
       </c>
       <c r="B1" s="25"/>
@@ -2204,7 +2219,7 @@
       <c r="F1" s="25"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="27" t="s">
         <v>66</v>
       </c>
       <c r="B2" s="25"/>
@@ -2625,7 +2640,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>92</v>
       </c>
       <c r="B1" s="25"/>
